--- a/data/trans_dic/P2A_lim_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 13,08</t>
+          <t>9,34; 13,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,8; 18,83</t>
+          <t>13,55; 18,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 13,25</t>
+          <t>8,87; 13,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,21; 29,25</t>
+          <t>22,25; 29,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,33; 13,89</t>
+          <t>10,36; 13,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,85; 18,06</t>
+          <t>13,85; 18,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,24; 18,12</t>
+          <t>13,37; 18,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,44; 29,03</t>
+          <t>24,44; 29,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,35; 12,97</t>
+          <t>10,42; 13,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,35; 17,59</t>
+          <t>14,36; 17,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,89; 15,24</t>
+          <t>11,95; 15,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,12; 28,18</t>
+          <t>24,59; 28,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,96</t>
+          <t>3,91; 6,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,68</t>
+          <t>6,04; 8,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 7,53</t>
+          <t>5,24; 7,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 13,14</t>
+          <t>8,0; 13,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,54</t>
+          <t>4,22; 6,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 10,61</t>
+          <t>7,86; 10,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 7,58</t>
+          <t>5,34; 7,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,69; 42,48</t>
+          <t>10,81; 44,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,88</t>
+          <t>4,37; 5,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 9,31</t>
+          <t>7,35; 9,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 7,22</t>
+          <t>5,6; 7,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,59; 29,45</t>
+          <t>10,52; 27,86</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,88</t>
+          <t>2,1; 5,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,63</t>
+          <t>3,28; 7,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,24</t>
+          <t>2,71; 6,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,38</t>
+          <t>6,81; 11,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,32</t>
+          <t>3,83; 8,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,4</t>
+          <t>5,36; 11,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,79</t>
+          <t>3,16; 7,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 9,94</t>
+          <t>6,07; 9,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,1</t>
+          <t>3,38; 6,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,44</t>
+          <t>4,93; 8,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,94</t>
+          <t>3,26; 5,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 10,19</t>
+          <t>6,99; 10,05</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,58</t>
+          <t>5,81; 7,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,52; 10,72</t>
+          <t>8,42; 10,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,02</t>
+          <t>6,1; 8,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 14,45</t>
+          <t>9,87; 14,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,11</t>
+          <t>7,1; 8,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 12,61</t>
+          <t>10,49; 12,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 9,8</t>
+          <t>7,79; 9,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,55; 31,22</t>
+          <t>13,75; 34,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,02</t>
+          <t>6,77; 8,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,79; 11,22</t>
+          <t>9,85; 11,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,6</t>
+          <t>7,24; 8,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,0; 23,55</t>
+          <t>13,04; 24,52</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95331; 134502</t>
+          <t>96031; 134185</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>134393; 183368</t>
+          <t>131944; 180347</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64612; 99772</t>
+          <t>66793; 102862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114063; 150192</t>
+          <t>114241; 150737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>135666; 182490</t>
+          <t>136110; 183498</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>185251; 241580</t>
+          <t>185292; 244352</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>131310; 179619</t>
+          <t>132616; 179231</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>184652; 219355</t>
+          <t>184682; 220744</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>242482; 303709</t>
+          <t>243953; 305503</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>331760; 406573</t>
+          <t>331914; 406099</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>207501; 265978</t>
+          <t>208590; 267546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>306138; 357663</t>
+          <t>312057; 358684</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65321; 100633</t>
+          <t>66078; 101863</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>123091; 170195</t>
+          <t>118491; 169862</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>107620; 155465</t>
+          <t>108297; 155559</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>177838; 299158</t>
+          <t>181957; 297906</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69095; 103669</t>
+          <t>66812; 103025</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>136142; 186236</t>
+          <t>138032; 188265</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>105212; 150536</t>
+          <t>106085; 150566</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>238073; 945946</t>
+          <t>240673; 991022</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>141495; 192394</t>
+          <t>143134; 196116</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>273660; 346197</t>
+          <t>273284; 342536</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>226586; 292438</t>
+          <t>226749; 293353</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>476951; 1326315</t>
+          <t>473912; 1254689</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11911; 32280</t>
+          <t>11531; 31782</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15381; 36727</t>
+          <t>15785; 38073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13975; 33849</t>
+          <t>14683; 33381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44386; 79179</t>
+          <t>43541; 76039</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18044; 39646</t>
+          <t>18264; 38807</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26223; 52293</t>
+          <t>24596; 51766</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17767; 37216</t>
+          <t>17303; 38746</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41103; 65060</t>
+          <t>39746; 63723</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34542; 62554</t>
+          <t>34638; 62334</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45240; 79365</t>
+          <t>46361; 78166</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36735; 64765</t>
+          <t>35562; 64114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91973; 131844</t>
+          <t>90481; 130059</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>189845; 247810</t>
+          <t>189776; 248188</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>291233; 366162</t>
+          <t>287559; 365751</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>209437; 269643</t>
+          <t>205075; 269529</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>341532; 495614</t>
+          <t>338553; 492754</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>241531; 307359</t>
+          <t>239778; 302984</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>369456; 447942</t>
+          <t>372773; 451948</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>275902; 345574</t>
+          <t>274749; 341924</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>492729; 1135461</t>
+          <t>500137; 1251266</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>448730; 532442</t>
+          <t>449897; 534914</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>682573; 782000</t>
+          <t>686539; 794704</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>499506; 592157</t>
+          <t>498412; 593264</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>918937; 1664310</t>
+          <t>921166; 1732337</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_lim_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,05</t>
+          <t>9,14; 13,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,55; 18,52</t>
+          <t>13,9; 18,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 13,66</t>
+          <t>9,08; 13,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,25; 29,35</t>
+          <t>21,03; 27,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 13,97</t>
+          <t>10,51; 13,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,85; 18,27</t>
+          <t>13,94; 18,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,37; 18,08</t>
+          <t>13,08; 18,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,44; 29,22</t>
+          <t>24,77; 29,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 13,04</t>
+          <t>10,4; 13,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,36; 17,57</t>
+          <t>14,36; 17,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,95; 15,33</t>
+          <t>11,89; 15,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,59; 28,26</t>
+          <t>23,92; 27,73</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -857,42 +857,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,03</t>
+          <t>3,99; 6,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,66</t>
+          <t>6,12; 8,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 7,53</t>
+          <t>5,38; 7,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,0; 13,09</t>
+          <t>10,87; 13,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,5</t>
+          <t>4,19; 6,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 10,72</t>
+          <t>7,83; 10,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 7,58</t>
+          <t>5,35; 7,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 44,5</t>
+          <t>10,8; 13,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 9,21</t>
+          <t>7,23; 9,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 7,24</t>
+          <t>5,58; 7,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 27,86</t>
+          <t>11,26; 13,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,78</t>
+          <t>2,17; 5,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,91</t>
+          <t>3,19; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,15</t>
+          <t>2,6; 6,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 11,89</t>
+          <t>7,07; 11,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 8,15</t>
+          <t>3,85; 8,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 11,29</t>
+          <t>5,47; 10,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,07</t>
+          <t>3,2; 7,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,73</t>
+          <t>6,27; 9,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,08</t>
+          <t>3,35; 6,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,32</t>
+          <t>4,85; 8,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,88</t>
+          <t>3,44; 6,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 10,05</t>
+          <t>7,08; 10,28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,6</t>
+          <t>5,79; 7,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 10,71</t>
+          <t>8,5; 10,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,02</t>
+          <t>6,17; 8,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,87; 14,37</t>
+          <t>12,39; 14,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,98</t>
+          <t>7,24; 9,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 12,72</t>
+          <t>10,25; 12,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 9,7</t>
+          <t>7,72; 9,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,75; 34,4</t>
+          <t>13,54; 15,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,05</t>
+          <t>6,75; 8,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 11,4</t>
+          <t>9,77; 11,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,62</t>
+          <t>7,24; 8,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,04; 24,52</t>
+          <t>13,3; 14,79</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130760</t>
+          <t>138891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>202486</t>
+          <t>220996</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>333246</t>
+          <t>359887</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>96031; 134185</t>
+          <t>93925; 133969</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131944; 180347</t>
+          <t>135329; 184019</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66793; 102862</t>
+          <t>68392; 101497</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114241; 150737</t>
+          <t>121370; 159003</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>136110; 183498</t>
+          <t>138134; 183604</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>185292; 244352</t>
+          <t>186434; 241483</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>132616; 179231</t>
+          <t>129725; 180495</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>184682; 220744</t>
+          <t>203619; 242105</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>243953; 305503</t>
+          <t>243681; 307192</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>331914; 406099</t>
+          <t>332003; 406459</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208590; 267546</t>
+          <t>207468; 266676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>312057; 358684</t>
+          <t>334675; 387907</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252047</t>
+          <t>270846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>431321</t>
+          <t>258928</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>683368</t>
+          <t>529775</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66078; 101863</t>
+          <t>67434; 102093</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118491; 169862</t>
+          <t>119978; 169813</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108297; 155559</t>
+          <t>111170; 157693</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181957; 297906</t>
+          <t>240383; 304930</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66812; 103025</t>
+          <t>66441; 103706</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>138032; 188265</t>
+          <t>137490; 187672</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>106085; 150566</t>
+          <t>106249; 151780</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>240673; 991022</t>
+          <t>233276; 287130</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>143134; 196116</t>
+          <t>143194; 196167</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>273284; 342536</t>
+          <t>268757; 339514</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>226749; 293353</t>
+          <t>225994; 293732</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>473912; 1254689</t>
+          <t>492135; 575273</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58696</t>
+          <t>64105</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51178</t>
+          <t>57473</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109874</t>
+          <t>121578</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11531; 31782</t>
+          <t>11931; 32505</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15785; 38073</t>
+          <t>15327; 36609</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14683; 33381</t>
+          <t>14118; 34916</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43541; 76039</t>
+          <t>49793; 83113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18264; 38807</t>
+          <t>18334; 40265</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24596; 51766</t>
+          <t>25108; 50322</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17303; 38746</t>
+          <t>17544; 38709</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39746; 63723</t>
+          <t>45660; 71223</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34638; 62334</t>
+          <t>34409; 64043</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46361; 78166</t>
+          <t>45607; 78134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35562; 64114</t>
+          <t>37500; 65480</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90481; 130059</t>
+          <t>101535; 147345</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>441503</t>
+          <t>473843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>684985</t>
+          <t>537397</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1126488</t>
+          <t>1011240</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>189776; 248188</t>
+          <t>189238; 250372</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>287559; 365751</t>
+          <t>290534; 362734</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205075; 269529</t>
+          <t>207356; 271037</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>338553; 492754</t>
+          <t>432825; 515766</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>239778; 302984</t>
+          <t>244338; 305926</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>372773; 451948</t>
+          <t>364053; 446458</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>274749; 341924</t>
+          <t>272177; 342558</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>500137; 1251266</t>
+          <t>502430; 574197</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>449897; 534914</t>
+          <t>448197; 532244</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>686539; 794704</t>
+          <t>681203; 789471</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>498412; 593264</t>
+          <t>498444; 588974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>921166; 1732337</t>
+          <t>957950; 1065769</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_lim_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica) (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica) (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
